--- a/docs/seguimiento/05_Inventario_Tecnico_y_Verificacion_Fase2.xlsx
+++ b/docs/seguimiento/05_Inventario_Tecnico_y_Verificacion_Fase2.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Inventario" sheetId="1" r:id="R3e8f4ed1e7d443e0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Estado_Tecnico" sheetId="2" r:id="R0b665ef31a314571"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Endpoints" sheetId="3" r:id="R6d80b962cafc44e3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Brechas" sheetId="4" r:id="R981d03bf16474076"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Inventario" sheetId="1" r:id="R5eedf0e5f1d54d94"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Estado_Tecnico" sheetId="2" r:id="Rd5a64ddc732a4014"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Endpoints" sheetId="3" r:id="R69fdd440e3354cdd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Brechas" sheetId="4" r:id="R7e618eab435743ab"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -453,10 +453,10 @@
         <x:v>Repositorio</x:v>
       </x:c>
       <x:c r="E6" s="15" t="str">
-        <x:v>PROBADO_PARCIAL</x:v>
+        <x:v>INTEGRADO_LOCAL</x:v>
       </x:c>
       <x:c r="F6" s="14" t="str">
-        <x:v>10 endpoints A en Docker; B/C conservan defectos abiertos.</x:v>
+        <x:v>A/B/C juntos en db6c916; E18 note y Stripe real pendientes.</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="30" customHeight="1">
@@ -475,10 +475,10 @@
         <x:v>Git</x:v>
       </x:c>
       <x:c r="E7" s="15" t="str">
-        <x:v>RAMA_LOCAL</x:v>
+        <x:v>INTEGRADO_LOCAL</x:v>
       </x:c>
       <x:c r="F7" s="12" t="str">
-        <x:v>equipo-a/backend-sprints; base c0bd41f; sin push.</x:v>
+        <x:v>codex/integracion-fase2; sin modificar origin/main ni publicar rama.</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="30" customHeight="1">
@@ -562,15 +562,11 @@
       <x:c r="D11" s="12" t="str">
         <x:v>URL y configuración</x:v>
       </x:c>
-      <x:c r="E11" s="15" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">PLANIFICADO</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F11" s="12" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Vercel, configuración pendiente.</x:t>
-        </x:is>
+      <x:c r="E11" s="15" t="str">
+        <x:v>LOCAL_VERIFICADO</x:v>
+      </x:c>
+      <x:c r="F11" s="12" t="str">
+        <x:v>Docker local y bases aisladas; Vercel no validado en esta revisión.</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="30" customHeight="1">
@@ -670,7 +666,7 @@
     </x:row>
     <x:row r="2" ht="24" customHeight="1">
       <x:c r="A2" s="18" t="str">
-        <x:v>Ejecución local al 29/09/2026. No acredita despliegue remoto ni aceptación docente.</x:v>
+        <x:v>Verificación local A/B/C al 20/10/2026. Sin despliegue ni aceptación académica.</x:v>
       </x:c>
       <x:c r="B2" s="18"/>
       <x:c r="C2" s="18"/>
@@ -734,10 +730,10 @@
         <x:v>Estructura, dependencias, ejecución y cobertura</x:v>
       </x:c>
       <x:c r="C7" s="12" t="str">
-        <x:v>PROBADO_PARCIAL</x:v>
+        <x:v>INTEGRADO_LOCAL</x:v>
       </x:c>
       <x:c r="D7" s="12" t="str">
-        <x:v>23 integración A + 5 unitarias; evidencias equipo-a</x:v>
+        <x:v>Regresión A/B/C; guía 04, db6c916. Pendientes note y Stripe real.</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="30" customHeight="1">
@@ -779,7 +775,7 @@
         <x:v>EJECUTADAS_LOCAL</x:v>
       </x:c>
       <x:c r="D10" s="14" t="str">
-        <x:v>43 aprobaciones / 50 ejecuciones; 7 fallos B/C. Incluye smoke repetida.</x:v>
+        <x:v>Regresión conjunta y contrato 8/8; proveedor Stripe simulado. Ver guía 04.</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="30" customHeight="1">
@@ -913,7 +909,7 @@
         <x:v>Consultar métricas generales</x:v>
       </x:c>
       <x:c r="G6" s="13" t="str">
-        <x:v>DEFINIDO_POR_CONTRATO</x:v>
+        <x:v>PROBADO_LOCAL / REVISION_PENDIENTE</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="30" customHeight="1">
@@ -936,7 +932,7 @@
         <x:v>Consultar métricas comerciales</x:v>
       </x:c>
       <x:c r="G7" s="13" t="str">
-        <x:v>DEFINIDO_POR_CONTRATO</x:v>
+        <x:v>PROBADO_LOCAL / REVISION_PENDIENTE</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="30" customHeight="1">
@@ -959,7 +955,7 @@
         <x:v>Listar patrocinadores</x:v>
       </x:c>
       <x:c r="G8" s="13" t="str">
-        <x:v>DEFINIDO_POR_CONTRATO</x:v>
+        <x:v>PROBADO_LOCAL / REVISION_PENDIENTE</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="30" customHeight="1">
@@ -982,7 +978,7 @@
         <x:v>Crear patrocinador</x:v>
       </x:c>
       <x:c r="G9" s="13" t="str">
-        <x:v>DEFINIDO_POR_CONTRATO</x:v>
+        <x:v>PROBADO_LOCAL / REVISION_PENDIENTE</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="30" customHeight="1">
@@ -1005,7 +1001,7 @@
         <x:v>Actualizar patrocinador</x:v>
       </x:c>
       <x:c r="G10" s="13" t="str">
-        <x:v>DEFINIDO_POR_CONTRATO</x:v>
+        <x:v>PROBADO_LOCAL / REVISION_PENDIENTE</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="30" customHeight="1">
@@ -1028,7 +1024,7 @@
         <x:v>Eliminar patrocinador</x:v>
       </x:c>
       <x:c r="G11" s="13" t="str">
-        <x:v>DEFINIDO_POR_CONTRATO</x:v>
+        <x:v>PROBADO_LOCAL / REVISION_PENDIENTE</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="30" customHeight="1">
@@ -1258,7 +1254,7 @@
         <x:v>Listar solicitudes de corrección</x:v>
       </x:c>
       <x:c r="G21" s="13" t="str">
-        <x:v>DEFINIDO_POR_CONTRATO</x:v>
+        <x:v>PROBADO_LOCAL / REVISION_PENDIENTE</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="30" customHeight="1">
@@ -1281,7 +1277,7 @@
         <x:v>Resolver solicitud de corrección</x:v>
       </x:c>
       <x:c r="G22" s="13" t="str">
-        <x:v>DEFINIDO_POR_CONTRATO</x:v>
+        <x:v>PARCIAL / NOTE_PENDIENTE</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="30" customHeight="1">
@@ -1304,7 +1300,7 @@
         <x:v>Listar preguntas</x:v>
       </x:c>
       <x:c r="G23" s="13" t="str">
-        <x:v>DEFINIDO_POR_CONTRATO</x:v>
+        <x:v>PROBADO_LOCAL / REVISION_PENDIENTE</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="30" customHeight="1">
@@ -1327,7 +1323,7 @@
         <x:v>Crear pregunta</x:v>
       </x:c>
       <x:c r="G24" s="13" t="str">
-        <x:v>DEFINIDO_POR_CONTRATO</x:v>
+        <x:v>PROBADO_LOCAL / REVISION_PENDIENTE</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="30" customHeight="1">
@@ -1350,7 +1346,7 @@
         <x:v>Actualizar pregunta</x:v>
       </x:c>
       <x:c r="G25" s="13" t="str">
-        <x:v>DEFINIDO_POR_CONTRATO</x:v>
+        <x:v>PROBADO_LOCAL / REVISION_PENDIENTE</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="30" customHeight="1">
@@ -1373,7 +1369,7 @@
         <x:v>Importar preguntas</x:v>
       </x:c>
       <x:c r="G26" s="13" t="str">
-        <x:v>DEFINIDO_POR_CONTRATO</x:v>
+        <x:v>PROBADO_LOCAL / REVISION_PENDIENTE</x:v>
       </x:c>
     </x:row>
     <x:row r="27" ht="30" customHeight="1">
@@ -1396,7 +1392,7 @@
         <x:v>Consultar funcionalidades</x:v>
       </x:c>
       <x:c r="G27" s="13" t="str">
-        <x:v>DEFINIDO_POR_CONTRATO</x:v>
+        <x:v>PROBADO_LOCAL / REVISION_PENDIENTE</x:v>
       </x:c>
     </x:row>
     <x:row r="28" ht="30" customHeight="1">
@@ -1419,7 +1415,7 @@
         <x:v>Listar planes</x:v>
       </x:c>
       <x:c r="G28" s="13" t="str">
-        <x:v>DEFINIDO_POR_CONTRATO</x:v>
+        <x:v>PROBADO_LOCAL / REVISION_PENDIENTE</x:v>
       </x:c>
     </x:row>
     <x:row r="29" ht="30" customHeight="1">
@@ -1442,7 +1438,7 @@
         <x:v>Crear plan</x:v>
       </x:c>
       <x:c r="G29" s="13" t="str">
-        <x:v>DEFINIDO_POR_CONTRATO</x:v>
+        <x:v>PROBADO_LOCAL / REVISION_PENDIENTE</x:v>
       </x:c>
     </x:row>
     <x:row r="30" ht="30" customHeight="1">
@@ -1465,7 +1461,7 @@
         <x:v>Actualizar plan</x:v>
       </x:c>
       <x:c r="G30" s="13" t="str">
-        <x:v>DEFINIDO_POR_CONTRATO</x:v>
+        <x:v>STRIPE_REAL_PENDIENTE</x:v>
       </x:c>
     </x:row>
     <x:row r="31" ht="30" customHeight="1">
@@ -1488,7 +1484,7 @@
         <x:v>Eliminar plan</x:v>
       </x:c>
       <x:c r="G31" s="13" t="str">
-        <x:v>DEFINIDO_POR_CONTRATO</x:v>
+        <x:v>PROBADO_LOCAL / REVISION_PENDIENTE</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1579,7 +1575,7 @@
         <x:v>Tsung-Hao</x:v>
       </x:c>
       <x:c r="F5" s="15" t="str">
-        <x:v>RAMA_LOCAL_PREPARADA</x:v>
+        <x:v>INTEGRADO_LOCAL</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="30" customHeight="1">
